--- a/driver.xlsx
+++ b/driver.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>driverName</t>
   </si>
@@ -19,382 +19,352 @@
     <t>driverNumber</t>
   </si>
   <si>
+    <t>Aadil Khan</t>
+  </si>
+  <si>
+    <t>8771205456</t>
+  </si>
+  <si>
     <t>Aarif Khan</t>
   </si>
   <si>
-    <t>8771205456</t>
-  </si>
-  <si>
-    <t>Abhishek Thakur</t>
-  </si>
-  <si>
     <t>8771205457</t>
   </si>
   <si>
+    <t>Abhishek Chouhan</t>
+  </si>
+  <si>
+    <t>8771205458</t>
+  </si>
+  <si>
     <t>Abhishek Vishwakarma</t>
   </si>
   <si>
-    <t>8771205458</t>
-  </si>
-  <si>
-    <t>Abhishekh Chouhan</t>
-  </si>
-  <si>
     <t>8771205459</t>
   </si>
   <si>
-    <t>Abhishekh Yadav</t>
+    <t>Abhishek Yadav</t>
   </si>
   <si>
     <t>8771205460</t>
   </si>
   <si>
-    <t>Ajay Bamniya</t>
+    <t>Amar Bahadur</t>
   </si>
   <si>
     <t>8771205461</t>
   </si>
   <si>
-    <t>Ajay Suryvanshi</t>
+    <t>Anokhi Lal Parmar</t>
   </si>
   <si>
     <t>8771205462</t>
   </si>
   <si>
-    <t>Amar Bahudar</t>
+    <t>Arjun Patel</t>
   </si>
   <si>
     <t>8771205463</t>
   </si>
   <si>
-    <t>Anokhi Solanki</t>
+    <t>Arman Khan</t>
   </si>
   <si>
     <t>8771205464</t>
   </si>
   <si>
-    <t>Arjun Patel</t>
+    <t>Bablu Rawat</t>
   </si>
   <si>
     <t>8771205465</t>
   </si>
   <si>
-    <t>Arman Khan</t>
+    <t>Balawant Singh</t>
   </si>
   <si>
     <t>8771205466</t>
   </si>
   <si>
-    <t>Arun Patel</t>
+    <t>Chandra Shekhar Chouhan</t>
   </si>
   <si>
     <t>8771205467</t>
   </si>
   <si>
-    <t>Ashok Tawar</t>
+    <t>Devkaran</t>
   </si>
   <si>
     <t>8771205468</t>
   </si>
   <si>
-    <t>Bablu Rawat</t>
+    <t>Devraj Singh</t>
   </si>
   <si>
     <t>8771205469</t>
   </si>
   <si>
-    <t>Balwant Singh</t>
+    <t>Dharmendra Yadav</t>
   </si>
   <si>
     <t>8771205470</t>
   </si>
   <si>
-    <t>Chandra Shekhar</t>
+    <t>Dinesh Kanse</t>
   </si>
   <si>
     <t>8771205471</t>
   </si>
   <si>
-    <t>Dashrath Singh</t>
+    <t>Farukh Khan</t>
   </si>
   <si>
     <t>8771205472</t>
   </si>
   <si>
-    <t>Devraj Singh</t>
+    <t>Hukum Patel</t>
   </si>
   <si>
     <t>8771205473</t>
   </si>
   <si>
-    <t>Dharmendra Yadav</t>
+    <t>Jitendra Dawar</t>
   </si>
   <si>
     <t>8771205474</t>
   </si>
   <si>
-    <t>Dinesh Kanse</t>
+    <t>Jitendra Nagar</t>
   </si>
   <si>
     <t>8771205475</t>
   </si>
   <si>
-    <t>Faruq Khan</t>
+    <t>Jitendra Sen</t>
   </si>
   <si>
     <t>8771205476</t>
   </si>
   <si>
-    <t>Govindra Sharma</t>
+    <t>Kailash Kumawat</t>
   </si>
   <si>
     <t>8771205477</t>
   </si>
   <si>
-    <t>Hukum Patel</t>
+    <t>Kalpesh Sisodiya</t>
   </si>
   <si>
     <t>8771205478</t>
   </si>
   <si>
-    <t>Ishwar Singh</t>
+    <t>Kamal Lodha</t>
   </si>
   <si>
     <t>8771205479</t>
   </si>
   <si>
-    <t>Jitendra Dawar</t>
+    <t>Kamal Prem Singh</t>
   </si>
   <si>
     <t>8771205480</t>
   </si>
   <si>
-    <t>Jitendra Jamre</t>
+    <t>Kamal Rathore</t>
   </si>
   <si>
     <t>8771205481</t>
   </si>
   <si>
-    <t>Jitendra Nagar</t>
+    <t>Khuman Singh</t>
   </si>
   <si>
     <t>8771205482</t>
   </si>
   <si>
-    <t>Jitendra Sen</t>
+    <t>Kishore Lodha</t>
   </si>
   <si>
     <t>8771205483</t>
   </si>
   <si>
-    <t>Kalpesh Sisodiya</t>
+    <t>Lakhan Sondhiya</t>
   </si>
   <si>
     <t>8771205484</t>
   </si>
   <si>
-    <t>Kamal Lodha</t>
+    <t>Lokesh Solanki</t>
   </si>
   <si>
     <t>8771205485</t>
   </si>
   <si>
-    <t>Kamal Rathore</t>
+    <t>Mahadev Yadav</t>
   </si>
   <si>
     <t>8771205486</t>
   </si>
   <si>
-    <t>Khuman Singh</t>
+    <t>Mahendra Prajapati</t>
   </si>
   <si>
     <t>8771205487</t>
   </si>
   <si>
-    <t>Kishore Lodha</t>
+    <t>Mohan Prajapati</t>
   </si>
   <si>
     <t>8771205488</t>
   </si>
   <si>
-    <t>Lokesh Solanki</t>
+    <t>Mohan Yadav</t>
   </si>
   <si>
     <t>8771205489</t>
   </si>
   <si>
-    <t>Mahadev Yadaw</t>
+    <t>Mukesh Dhakad</t>
   </si>
   <si>
     <t>8771205490</t>
   </si>
   <si>
-    <t>Mahendra Kumar</t>
+    <t>Nishar Khan</t>
   </si>
   <si>
     <t>8771205491</t>
   </si>
   <si>
-    <t>Meherban Singh</t>
+    <t>Poonam Chand</t>
   </si>
   <si>
     <t>8771205492</t>
   </si>
   <si>
-    <t>Mohan Prajapati</t>
+    <t>Prakash Keer</t>
   </si>
   <si>
     <t>8771205493</t>
   </si>
   <si>
-    <t>Mohan Yadav</t>
+    <t>Prakesh Engle</t>
   </si>
   <si>
     <t>8771205494</t>
   </si>
   <si>
-    <t>Mukesh Dhakad</t>
+    <t>Rahul Dawar</t>
   </si>
   <si>
     <t>8771205495</t>
   </si>
   <si>
-    <t>Mukesh Waskale</t>
+    <t>Rahul Solanki</t>
   </si>
   <si>
     <t>8771205496</t>
   </si>
   <si>
-    <t>Nishar Khan</t>
+    <t>Rais Khan</t>
   </si>
   <si>
     <t>8771205497</t>
   </si>
   <si>
-    <t>Poonam Chandra</t>
+    <t>Rajesh Prajapati</t>
   </si>
   <si>
     <t>8771205498</t>
   </si>
   <si>
-    <t>Prakash Keer</t>
+    <t>Rajesh Rathore</t>
   </si>
   <si>
     <t>8771205499</t>
   </si>
   <si>
-    <t>Prem Kamal</t>
+    <t>Rakesh Patel</t>
   </si>
   <si>
     <t>8771205500</t>
   </si>
   <si>
-    <t>Rafik Khan</t>
+    <t>Ramcharan</t>
   </si>
   <si>
     <t>8771205501</t>
   </si>
   <si>
-    <t>Rahul Dawar</t>
+    <t>Ritesh Prajapati</t>
   </si>
   <si>
     <t>8771205502</t>
   </si>
   <si>
-    <t>Rajesh Rathore</t>
+    <t>Salamat Ali</t>
   </si>
   <si>
     <t>8771205503</t>
   </si>
   <si>
-    <t>Ritesh Prajapati</t>
+    <t>Shekhar Mandhwa</t>
   </si>
   <si>
     <t>8771205504</t>
   </si>
   <si>
-    <t>Rohit Bhargwa</t>
+    <t>Shiva Chouhan</t>
   </si>
   <si>
     <t>8771205505</t>
   </si>
   <si>
-    <t>Sakti Raj</t>
+    <t>Sukul Patel</t>
   </si>
   <si>
     <t>8123401001</t>
   </si>
   <si>
-    <t>Salamat Ali</t>
+    <t>Suneel Chohan</t>
   </si>
   <si>
     <t>8123401002</t>
   </si>
   <si>
-    <t>Santosh Prajapati</t>
+    <t>Suresh Bhati</t>
   </si>
   <si>
     <t>8123401003</t>
   </si>
   <si>
-    <t>Shaktiraj</t>
+    <t>Vijay Kumawat</t>
   </si>
   <si>
     <t>8123401004</t>
   </si>
   <si>
-    <t>Shekhar Madhwa</t>
+    <t>Vishal Makwana</t>
   </si>
   <si>
     <t>8123401005</t>
   </si>
   <si>
-    <t>Shekhar Patel</t>
+    <t>Vishnu Patidar</t>
   </si>
   <si>
     <t>8123401006</t>
   </si>
   <si>
-    <t>Sohan Singh</t>
-  </si>
-  <si>
-    <t>8123401007</t>
-  </si>
-  <si>
-    <t>Sonu Rajput</t>
-  </si>
-  <si>
-    <t>8123401008</t>
-  </si>
-  <si>
-    <t>Suneel Chouhan</t>
-  </si>
-  <si>
-    <t>8123401009</t>
-  </si>
-  <si>
-    <t>Suresh Bhati</t>
-  </si>
-  <si>
-    <t>8123401010</t>
-  </si>
-  <si>
-    <t>Tulsiram</t>
-  </si>
-  <si>
-    <t>8123401011</t>
-  </si>
-  <si>
-    <t>Vijay Kumawat</t>
-  </si>
-  <si>
-    <t>8123401012</t>
-  </si>
-  <si>
-    <t>Vishal Kumar-Kamal</t>
-  </si>
-  <si>
-    <t>8123401013</t>
+    <t>Pankaj Aalpuriya</t>
+  </si>
+  <si>
+    <t>8964864049</t>
+  </si>
+  <si>
+    <t>Shubham Vishwakarma</t>
+  </si>
+  <si>
+    <t>8225905838</t>
   </si>
 </sst>
 </file>
@@ -771,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1250,46 +1220,6 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" t="s">
-        <v>127</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
